--- a/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:23</t>
+          <t>2026-08-26 16:01:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:27</t>
+          <t>2026-08-26 16:01:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:28</t>
+          <t>2026-08-26 16:01:13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:29</t>
+          <t>2026-08-26 16:01:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:29</t>
+          <t>2026-08-26 16:01:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:29</t>
+          <t>2026-08-26 16:01:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:29</t>
+          <t>2026-08-26 16:01:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:29</t>
+          <t>2026-08-26 16:01:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:29</t>
+          <t>2026-08-26 16:01:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.63%2415</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.63%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2415</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.09%11,884,000</t>
+          <t>9.90%11,884,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.09%</t>
+          <t>9.90%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +572,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+5.36%5895</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+5.36%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5895</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.59%4,843,000</t>
+          <t>9.85%4,843,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.59%</t>
+          <t>9.85%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +635,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+5.94%1160</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+5.94%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1160</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.86%20,300,000</t>
+          <t>8.12%20,300,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.86%</t>
+          <t>8.12%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +698,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.62%3945</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.62%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3945</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.80%5,148,000</t>
+          <t>7.01%5,148,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.80%</t>
+          <t>7.01%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,33 +761,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+6.95%3155</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+6.95%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3155</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.16%5,899,000</t>
+          <t>6.51%5,979,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>6.51%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5899000</v>
+        <v>5979000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +824,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+5.36%6785</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+5.36%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>6785</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.07%2,226,000</t>
+          <t>5.21%2,226,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.07%</t>
+          <t>5.21%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +882,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-10%5040</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>5040</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.93%2,486,000</t>
+          <t>4.75%2,407,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>4.75%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2486000</v>
+        <v>2407000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +950,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.29%537</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.29%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>537</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.89%25,387,000</t>
+          <t>4.70%25,387,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>4.70%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +1013,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.23%2055</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.23%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>2055</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.71%6,564,000</t>
+          <t>4.65%6,564,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>4.65%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1071,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+9.99%5725</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+9.99%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>5725</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.43%2,407,000</t>
+          <t>4.32%2,486,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.43%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2407000</v>
+        <v>2486000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1139,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.34%1750</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.34%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1750</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.26%7,040,000</t>
+          <t>4.25%7,040,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1202,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.17%592</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.17%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>592</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.07%19,479,000</t>
+          <t>3.98%19,479,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>3.98%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1260,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.2%123.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.2%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>123.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.96%89,518,000</t>
+          <t>3.92%9,624,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>89518000</v>
+        <v>9624000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1323,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.72%1180</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.72%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1180</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.95%9,624,000</t>
+          <t>3.81%89,518,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.81%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>9624000</v>
+        <v>89518000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:08</t>
+          <t>2026-08-26 17:22:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1391,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.37%2005</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.37%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2005</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.43%4,671,848</t>
+          <t>3.23%4,671,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1439,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.89%5,498,000</t>
+          <t>2.90%5,498,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1502,12 +1532,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.09%383,900</t>
+          <t>2.08%383,900</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1565,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.48%2,264,000</t>
+          <t>1.58%2,264,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1578,7 +1608,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1628,12 +1658,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.96%11,275,450</t>
+          <t>0.95%11,275,450</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1691,12 +1721,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.85%2,477,000</t>
+          <t>0.83%2,477,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1754,12 +1784,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.67%1,957,000</t>
+          <t>0.70%1,957,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1797,40 +1827,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.65%1195</t>
+          <t>+9.96%6125</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>+9.96%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.56%1,301,000</t>
+          <t>0.69%325,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1301000</v>
+        <v>325000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,40 +1890,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.5%598</t>
+          <t>-1.65%1195</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.52%2,424,000</t>
+          <t>0.54%1,301,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2424000</v>
+        <v>1301000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1923,27 +1953,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+9.96%6125</t>
+          <t>-0.5%598</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>598</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.50%255,000</t>
+          <t>0.50%2,424,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1952,11 +1982,11 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>255000</v>
+        <v>2424000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2006,12 +2036,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.45%5,917,000</t>
+          <t>0.44%5,917,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2069,12 +2099,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.45%477,000</t>
+          <t>0.43%477,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2175,27 +2205,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+2.36%1300</t>
+          <t>+9.92%199.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>+9.92%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.22%483,000</t>
+          <t>0.22%3,249,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2204,11 +2234,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>483000</v>
+        <v>3249000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:11</t>
+          <t>2026-08-26 17:22:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2238,40 +2268,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+9.92%199.5</t>
+          <t>+2.36%1300</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.21%3,249,000</t>
+          <t>0.22%483,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>3249000</v>
+        <v>483000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:13</t>
+          <t>2026-08-26 17:22:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:14</t>
+          <t>2026-08-26 17:22:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:14</t>
+          <t>2026-08-26 17:22:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:14</t>
+          <t>2026-08-26 17:22:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:14</t>
+          <t>2026-08-26 17:22:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:14</t>
+          <t>2026-08-26 17:22:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:14</t>
+          <t>2026-08-26 17:22:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.63%2415</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2415</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.36%5895</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.36%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5895</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.94%1160</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.94%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1160</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.62%3945</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.62%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3945</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+6.95%3155</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+6.95%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3155</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.36%6785</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.36%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6785</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.99%5725</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5725</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.29%537</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>537</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.23%2055</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.23%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2055</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-10%5040</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5040</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.34%1750</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.34%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1750</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.17%592</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>592</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.72%1180</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.72%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1180</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.2%123.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.2%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>123.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:36</t>
+          <t>2026-08-26 19:33:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.37%2005</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.37%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2005</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:41</t>
+          <t>2026-08-26 19:33:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:42</t>
+          <t>2026-08-26 19:33:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:43</t>
+          <t>2026-08-26 19:33:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:43</t>
+          <t>2026-08-26 19:33:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:43</t>
+          <t>2026-08-26 19:33:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:43</t>
+          <t>2026-08-26 19:33:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:43</t>
+          <t>2026-08-26 19:33:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 17:22:43</t>
+          <t>2026-08-26 19:33:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:40</t>
+          <t>2026-08-26 21:13:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:41</t>
+          <t>2026-08-26 21:14:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:43</t>
+          <t>2026-08-26 21:14:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:44</t>
+          <t>2026-08-26 21:14:26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:44</t>
+          <t>2026-08-26 21:14:26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:44</t>
+          <t>2026-08-26 21:14:26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:44</t>
+          <t>2026-08-26 21:14:26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:44</t>
+          <t>2026-08-26 21:14:26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 19:33:44</t>
+          <t>2026-08-26 21:14:26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 21:13:52</t>
+          <t>2026-08-26 21:37:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:03</t>
+          <t>2026-08-26 21:37:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:15</t>
+          <t>2026-08-26 21:37:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:26</t>
+          <t>2026-08-26 21:37:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:26</t>
+          <t>2026-08-26 21:37:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:26</t>
+          <t>2026-08-26 21:37:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:26</t>
+          <t>2026-08-26 21:37:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:26</t>
+          <t>2026-08-26 21:37:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:26</t>
+          <t>2026-08-26 21:37:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.63%2415</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.63%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2415</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+5.36%5895</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+5.36%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5895</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+5.94%1160</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+5.94%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1160</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.62%3945</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.62%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3945</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+6.95%3155</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+6.95%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3155</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+5.36%6785</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+5.36%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>6785</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+9.99%5725</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+9.99%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>5725</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.29%537</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.29%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>537</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.23%2055</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.23%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>2055</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-10%5040</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>5040</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.34%1750</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.34%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1750</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.17%592</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.17%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>592</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+1.72%1180</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+1.72%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1180</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.2%123.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.2%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>123.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:41</t>
+          <t>2026-08-26 22:04:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.37%2005</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.37%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2005</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:42</t>
+          <t>2026-08-26 22:04:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:44</t>
+          <t>2026-08-26 22:05:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:45</t>
+          <t>2026-08-26 22:05:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:45</t>
+          <t>2026-08-26 22:05:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:45</t>
+          <t>2026-08-26 22:05:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:45</t>
+          <t>2026-08-26 22:05:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:45</t>
+          <t>2026-08-26 22:05:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 21:37:45</t>
+          <t>2026-08-26 22:05:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:46</t>
+          <t>2026-08-26 22:13:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 22:04:59</t>
+          <t>2026-08-26 22:13:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:10</t>
+          <t>2026-08-26 22:13:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:21</t>
+          <t>2026-08-26 22:13:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:21</t>
+          <t>2026-08-26 22:13:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:21</t>
+          <t>2026-08-26 22:13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:21</t>
+          <t>2026-08-26 22:13:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:21</t>
+          <t>2026-08-26 22:13:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 22:05:21</t>
+          <t>2026-08-26 22:13:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.63%2415</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2415</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.36%5895</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.36%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5895</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.94%1160</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.94%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1160</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.62%3945</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.62%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3945</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+6.95%3155</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+6.95%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3155</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.36%6785</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.36%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6785</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.99%5725</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5725</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.29%537</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>537</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.23%2055</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.23%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2055</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-10%5040</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5040</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.34%1750</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.34%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1750</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.17%592</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>592</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.72%1180</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.72%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1180</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.2%123.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.2%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>123.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:23</t>
+          <t>2026-08-26 22:18:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.37%2005</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.37%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2005</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:28</t>
+          <t>2026-08-26 22:18:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:29</t>
+          <t>2026-08-26 22:18:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:30</t>
+          <t>2026-08-26 22:18:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:30</t>
+          <t>2026-08-26 22:18:53</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:30</t>
+          <t>2026-08-26 22:18:53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:30</t>
+          <t>2026-08-26 22:18:53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:30</t>
+          <t>2026-08-26 22:18:53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 22:13:30</t>
+          <t>2026-08-26 22:18:53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
